--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98215</v>
+        <v>98216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79166</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98216</v>
+        <v>98222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91478</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98222</v>
+        <v>98226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98226</v>
+        <v>98228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79172</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98230</v>
+        <v>98243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79172</v>
+        <v>79185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79185</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98245</v>
+        <v>98248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91502</v>
+        <v>91512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98248</v>
+        <v>98258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98259</v>
+        <v>98264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79197</v>
+        <v>79200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98264</v>
+        <v>98266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91518</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79200</v>
+        <v>79205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98272</v>
+        <v>98284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79205</v>
+        <v>79216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98284</v>
+        <v>98285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79216</v>
+        <v>79217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98285</v>
+        <v>98288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79217</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35055-2026 artfynd.xlsx
+++ b/artfynd/A 35055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137088823</v>
       </c>
       <c r="B2" t="n">
-        <v>91539</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>137088503</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>137088799</v>
       </c>
       <c r="B4" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137088893</v>
       </c>
       <c r="B5" t="n">
-        <v>98288</v>
+        <v>98292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>137088900</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
